--- a/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -540,10 +540,9 @@
           <t>+385 21 532 570</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distribuzione utensili elettrici/manuali, ricambi e accessori (Makita, Bosch, Rems, Hilti, Stanley), servizio assistenza. Sede principale a Zagabria con filiale Split. Email generica non trovata.</t>
+          <t>Distribuzione utensili elettrici/manuali, ricambi e accessori (Makita, Bosch, Rems, Hilti, Stanley), servizio assistenza. Sede principale a Zagabria con filiale Split. Email generica non trovata. [DUPLICATO — vedi anche: 2026-09-20_12_Croazia_Splitsko-dalmatinska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Distributore compressori (Kaeser, CompAir, Fini, Trudbenik, GGA), utensili officina (Samoa, Gedore, Unior, Hazet, Knipex), pneumatica/idraulica industriale. Include anche ricambi veicoli commerciali.</t>
+          <t>Distributore compressori (Kaeser, CompAir, Fini, Trudbenik, GGA), utensili officina (Samoa, Gedore, Unior, Hazet, Knipex), pneumatica/idraulica industriale. Include anche ricambi veicoli commerciali. [DUPLICATO — vedi anche: 2026-09-20_13_Croazia_Splitsko-dalmatinska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Commercio semilavorati siderurgici e metalli non ferrosi, acciai inox, cuscinetti, utensili, attrezzature per saldatura, tecnologia di fissaggio. Filiale Split denominata 'Metal Centar Split', Put Brižina 11.</t>
+          <t>Commercio semilavorati siderurgici e metalli non ferrosi, acciai inox, cuscinetti, utensili, attrezzature per saldatura, tecnologia di fissaggio. Filiale Split denominata 'Metal Centar Split', Put Brižina 11. [DUPLICATO — vedi anche: 2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Forniture industriali, utensili, attrezzature officina, sistemi di stoccaggio. Pienamente confermato tramite WebSearch (eshop.wuerth.com.hr, wuerth.com.hr).</t>
+          <t>Forniture industriali, utensili, attrezzature officina, sistemi di stoccaggio. Pienamente confermato tramite WebSearch (eshop.wuerth.com.hr, wuerth.com.hr). [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
